--- a/dados_entrada.xlsx
+++ b/dados_entrada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\loteamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0398F3C-3CE3-4DEF-A47E-8E4B8761BCB5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4058AD4A-0681-4FFE-BE76-86D255F5126B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{580E5A1F-D7D8-443D-8430-D21E3EA9E741}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Nome</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>O lote de terreno sob nº 47 da Quadra 01, integrante do Loteamento denominado "CARMELITA ARRIEIRO" situado a Avenida Carmelita Arrieiro, no município de CURVELO - MG, possui os seguintes limites e confrontações: Inicia-se a descrição deste perímetro no ponto 1 com coordenada (E: 561202.535 N: 7922702.516), com uma distância de 21.53 m confrontando com o Lote 48 com azimute de 350º28'2.28'' até o ponto 2 com coordenada (E: 561198.969 N: 7922723.754), com uma distância de 9.63 m confrontando com o Lote 44 com azimute de 78º46'27.12'' até o ponto 3 com coordenada (E: 561208.419 N: 7922725.629), com uma distância de 21.61 m confrontando com o Lote 46 com azimute de 168º12'37.08'' até o ponto 4 com coordenada (E: 561212.834 N: 7922704.476), com uma distância de 10.48 m confrontando com a Avenida Carmelita Arrieiro com azimute de 259º13'42.60'' até o ponto 1 com coordenada (E: 561202.535 N: 7922702.516). Todas as coordenadas aqui descritas estão georreferenciadas e encontram-se representadas no Sistema UTM e no Fuso 23K, hemisfério sul, referenciadas ao Meridiano Central nº -45º, tendo como Datum SIRGAS 2000.</t>
+  </si>
+  <si>
+    <t>Endereço</t>
   </si>
 </sst>
 </file>
@@ -465,92 +468,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20799440-8B72-46E7-92F7-92155D756C49}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.28515625" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" hidden="1"/>
+    <col min="3" max="3" width="122.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="str">
+        <f>"\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\"&amp;LEFT(A2,9)&amp;"\"&amp;RIGHT(A2,LEN(A2)-12)</f>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 40A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="str">
+        <f t="shared" ref="C3:C15" si="0">"\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\"&amp;LEFT(A3,9)&amp;"\"&amp;RIGHT(A3,LEN(A3)-12)</f>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 42A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>\\192.168.1.1\Rede Cartorio\5 Registro\Plotagem\DIMENSOR - BEM TOPOGRAFIA\REURB - CARMELITA ARRIEIRO\QUADRA 01\LOTE 47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
